--- a/artfynd/A 22547-2026 artfynd.xlsx
+++ b/artfynd/A 22547-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,6 +1049,3690 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133505440</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>636418</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6668890</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133505416</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>636238</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6668537</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133505428</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92378</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>636407</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6668568</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133505439</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>636429</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6668832</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133505431</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>636331</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6668637</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133505445</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>636385</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6669003</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133505455</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>636195</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6669061</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133505437</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>636297</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6668845</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133505421</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>636195</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668569</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133505415</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>636248</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668556</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133505435</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>636337</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6668680</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133505418</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>308</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>636240</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668551</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133505452</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>636195</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6669061</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133505442</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>636397</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668963</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133505429</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>636385</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668569</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133505425</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>636402</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6668607</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133505427</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>636407</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668568</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133505458</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97370</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>636122</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6669062</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133505450</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97370</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>53</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>636193</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6669060</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133505424</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>636299</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6668569</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133505434</v>
+      </c>
+      <c r="B25" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>308</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>636321</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6668644</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133505438</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>636305</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6668862</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133505441</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>636414</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6668891</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133505417</v>
+      </c>
+      <c r="B28" t="n">
+        <v>83298</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>636242</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6668543</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133505436</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>636209</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6668786</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133505420</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>636224</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6668560</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133505444</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>636416</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6668962</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133505459</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>636129</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6668995</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133505449</v>
+      </c>
+      <c r="B33" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>636189</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6669067</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133505453</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>636195</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6669061</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133505419</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>636240</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6668551</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133505422</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>636213</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6668594</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133505423</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>636265</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6668598</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133505446</v>
+      </c>
+      <c r="B38" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>308</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>636243</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6669054</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22547-2026 artfynd.xlsx
+++ b/artfynd/A 22547-2026 artfynd.xlsx
@@ -1158,32 +1158,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133505416</v>
+        <v>133505428</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>92378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636238</v>
+        <v>636407</v>
       </c>
       <c r="R6" t="n">
-        <v>6668537</v>
+        <v>6668568</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,32 +1265,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133505428</v>
+        <v>133505416</v>
       </c>
       <c r="B7" t="n">
-        <v>92378</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636407</v>
+        <v>636238</v>
       </c>
       <c r="R7" t="n">
-        <v>6668568</v>
+        <v>6668537</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1591,32 +1591,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133505445</v>
+        <v>133505437</v>
       </c>
       <c r="B10" t="n">
-        <v>8444</v>
+        <v>5178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>102204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636385</v>
+        <v>636297</v>
       </c>
       <c r="R10" t="n">
-        <v>6669003</v>
+        <v>6668845</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,32 +1698,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133505455</v>
+        <v>133505415</v>
       </c>
       <c r="B11" t="n">
-        <v>5199</v>
+        <v>58119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636195</v>
+        <v>636248</v>
       </c>
       <c r="R11" t="n">
-        <v>6669061</v>
+        <v>6668556</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,32 +1810,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133505437</v>
+        <v>133505445</v>
       </c>
       <c r="B12" t="n">
-        <v>5178</v>
+        <v>8444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102204</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636297</v>
+        <v>636385</v>
       </c>
       <c r="R12" t="n">
-        <v>6668845</v>
+        <v>6669003</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133505421</v>
+        <v>133505455</v>
       </c>
       <c r="B13" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1950,7 +1955,7 @@
         <v>636195</v>
       </c>
       <c r="R13" t="n">
-        <v>6668569</v>
+        <v>6669061</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,32 +2024,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133505415</v>
+        <v>133505421</v>
       </c>
       <c r="B14" t="n">
-        <v>58119</v>
+        <v>8444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636248</v>
+        <v>636195</v>
       </c>
       <c r="R14" t="n">
-        <v>6668556</v>
+        <v>6668569</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2089,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,12 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,32 +2131,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133505435</v>
+        <v>133505418</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636337</v>
+        <v>636240</v>
       </c>
       <c r="R15" t="n">
-        <v>6668680</v>
+        <v>6668551</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133505418</v>
+        <v>133505435</v>
       </c>
       <c r="B16" t="n">
-        <v>83307</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636240</v>
+        <v>636337</v>
       </c>
       <c r="R16" t="n">
-        <v>6668551</v>
+        <v>6668680</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133505452</v>
+        <v>133505429</v>
       </c>
       <c r="B17" t="n">
-        <v>5178</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636195</v>
+        <v>636385</v>
       </c>
       <c r="R17" t="n">
-        <v>6669061</v>
+        <v>6668569</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133505442</v>
+        <v>133505452</v>
       </c>
       <c r="B18" t="n">
-        <v>91939</v>
+        <v>5178</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>102204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636397</v>
+        <v>636195</v>
       </c>
       <c r="R18" t="n">
-        <v>6668963</v>
+        <v>6669061</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2522,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133505429</v>
+        <v>133505442</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636385</v>
+        <v>636397</v>
       </c>
       <c r="R19" t="n">
-        <v>6668569</v>
+        <v>6668963</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2629,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,12 +2644,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2893,10 +2893,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133505458</v>
+        <v>133505424</v>
       </c>
       <c r="B22" t="n">
-        <v>97370</v>
+        <v>57955</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636122</v>
+        <v>636299</v>
       </c>
       <c r="R22" t="n">
-        <v>6669062</v>
+        <v>6668569</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2973,7 +2973,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133505450</v>
+        <v>133505434</v>
       </c>
       <c r="B23" t="n">
-        <v>97370</v>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,21 +3016,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3035,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636193</v>
+        <v>636321</v>
       </c>
       <c r="R23" t="n">
-        <v>6669060</v>
+        <v>6668644</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3070,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3080,7 +3085,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,10 +3112,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133505424</v>
+        <v>133505458</v>
       </c>
       <c r="B24" t="n">
-        <v>57955</v>
+        <v>97370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3118,21 +3123,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3142,10 +3147,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636299</v>
+        <v>636122</v>
       </c>
       <c r="R24" t="n">
-        <v>6668569</v>
+        <v>6669062</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3177,7 +3182,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3187,12 +3192,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,10 +3219,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133505434</v>
+        <v>133505450</v>
       </c>
       <c r="B25" t="n">
-        <v>83307</v>
+        <v>97370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636321</v>
+        <v>636193</v>
       </c>
       <c r="R25" t="n">
-        <v>6668644</v>
+        <v>6669060</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,32 +3433,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133505441</v>
+        <v>133505417</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>83298</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636414</v>
+        <v>636242</v>
       </c>
       <c r="R27" t="n">
-        <v>6668891</v>
+        <v>6668543</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3540,32 +3540,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133505417</v>
+        <v>133505441</v>
       </c>
       <c r="B28" t="n">
-        <v>83298</v>
+        <v>57955</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636242</v>
+        <v>636414</v>
       </c>
       <c r="R28" t="n">
-        <v>6668543</v>
+        <v>6668891</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3647,32 +3647,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133505436</v>
+        <v>133505420</v>
       </c>
       <c r="B29" t="n">
-        <v>8444</v>
+        <v>58119</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636209</v>
+        <v>636224</v>
       </c>
       <c r="R29" t="n">
-        <v>6668786</v>
+        <v>6668560</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3727,7 +3727,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,32 +3759,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133505420</v>
+        <v>133505436</v>
       </c>
       <c r="B30" t="n">
-        <v>58119</v>
+        <v>8444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3789,10 +3794,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636224</v>
+        <v>636209</v>
       </c>
       <c r="R30" t="n">
-        <v>6668560</v>
+        <v>6668786</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3824,7 +3829,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3834,12 +3839,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4409,10 +4409,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133505422</v>
+        <v>133505446</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636213</v>
+        <v>636243</v>
       </c>
       <c r="R36" t="n">
-        <v>6668594</v>
+        <v>6669054</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4489,12 +4489,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4521,10 +4516,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133505423</v>
+        <v>133505422</v>
       </c>
       <c r="B37" t="n">
-        <v>5178</v>
+        <v>57955</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4532,21 +4527,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4556,10 +4551,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636265</v>
+        <v>636213</v>
       </c>
       <c r="R37" t="n">
-        <v>6668598</v>
+        <v>6668594</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4591,7 +4586,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4601,7 +4596,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4628,10 +4628,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133505446</v>
+        <v>133505423</v>
       </c>
       <c r="B38" t="n">
-        <v>83307</v>
+        <v>5178</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4639,21 +4639,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>102204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636243</v>
+        <v>636265</v>
       </c>
       <c r="R38" t="n">
-        <v>6669054</v>
+        <v>6668598</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 22547-2026 artfynd.xlsx
+++ b/artfynd/A 22547-2026 artfynd.xlsx
@@ -1158,32 +1158,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133505428</v>
+        <v>133505416</v>
       </c>
       <c r="B6" t="n">
-        <v>92378</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636407</v>
+        <v>636238</v>
       </c>
       <c r="R6" t="n">
-        <v>6668568</v>
+        <v>6668537</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,32 +1265,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133505416</v>
+        <v>133505428</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>92378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636238</v>
+        <v>636407</v>
       </c>
       <c r="R7" t="n">
-        <v>6668537</v>
+        <v>6668568</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133505429</v>
+        <v>133505442</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636385</v>
+        <v>636397</v>
       </c>
       <c r="R17" t="n">
-        <v>6668569</v>
+        <v>6668963</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,12 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133505452</v>
+        <v>133505429</v>
       </c>
       <c r="B18" t="n">
-        <v>5178</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636195</v>
+        <v>636385</v>
       </c>
       <c r="R18" t="n">
-        <v>6669061</v>
+        <v>6668569</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2527,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2532,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133505442</v>
+        <v>133505452</v>
       </c>
       <c r="B19" t="n">
-        <v>91939</v>
+        <v>5178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>102204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636397</v>
+        <v>636195</v>
       </c>
       <c r="R19" t="n">
-        <v>6668963</v>
+        <v>6669061</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3005,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133505434</v>
+        <v>133505450</v>
       </c>
       <c r="B23" t="n">
-        <v>83307</v>
+        <v>97370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,21 +3016,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636321</v>
+        <v>636193</v>
       </c>
       <c r="R23" t="n">
-        <v>6668644</v>
+        <v>6669060</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,10 +3219,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133505450</v>
+        <v>133505434</v>
       </c>
       <c r="B25" t="n">
-        <v>97370</v>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636193</v>
+        <v>636321</v>
       </c>
       <c r="R25" t="n">
-        <v>6669060</v>
+        <v>6668644</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133505417</v>
+        <v>133505436</v>
       </c>
       <c r="B27" t="n">
-        <v>83298</v>
+        <v>8444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636242</v>
+        <v>636209</v>
       </c>
       <c r="R27" t="n">
-        <v>6668543</v>
+        <v>6668786</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3540,32 +3540,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133505441</v>
+        <v>133505417</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>83298</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636414</v>
+        <v>636242</v>
       </c>
       <c r="R28" t="n">
-        <v>6668891</v>
+        <v>6668543</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3647,10 +3647,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133505420</v>
+        <v>133505441</v>
       </c>
       <c r="B29" t="n">
-        <v>58119</v>
+        <v>57955</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636224</v>
+        <v>636414</v>
       </c>
       <c r="R29" t="n">
-        <v>6668560</v>
+        <v>6668891</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3727,12 +3727,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3759,32 +3754,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133505436</v>
+        <v>133505420</v>
       </c>
       <c r="B30" t="n">
-        <v>8444</v>
+        <v>58119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3794,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636209</v>
+        <v>636224</v>
       </c>
       <c r="R30" t="n">
-        <v>6668786</v>
+        <v>6668560</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3829,7 +3824,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3839,7 +3834,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 22547-2026 artfynd.xlsx
+++ b/artfynd/A 22547-2026 artfynd.xlsx
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133505431</v>
+        <v>133505415</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>58119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636331</v>
+        <v>636248</v>
       </c>
       <c r="R9" t="n">
-        <v>6668637</v>
+        <v>6668556</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133505415</v>
+        <v>133505431</v>
       </c>
       <c r="B11" t="n">
-        <v>58119</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636248</v>
+        <v>636331</v>
       </c>
       <c r="R11" t="n">
-        <v>6668556</v>
+        <v>6668637</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133505455</v>
+        <v>133505421</v>
       </c>
       <c r="B13" t="n">
-        <v>5199</v>
+        <v>8444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
         <v>636195</v>
       </c>
       <c r="R13" t="n">
-        <v>6669061</v>
+        <v>6668569</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133505421</v>
+        <v>133505455</v>
       </c>
       <c r="B14" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         <v>636195</v>
       </c>
       <c r="R14" t="n">
-        <v>6668569</v>
+        <v>6669061</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133505442</v>
+        <v>133505429</v>
       </c>
       <c r="B17" t="n">
-        <v>91939</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636397</v>
+        <v>636385</v>
       </c>
       <c r="R17" t="n">
-        <v>6668963</v>
+        <v>6668569</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133505429</v>
+        <v>133505442</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636385</v>
+        <v>636397</v>
       </c>
       <c r="R18" t="n">
-        <v>6668569</v>
+        <v>6668963</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2522,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,12 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133505425</v>
+        <v>133505427</v>
       </c>
       <c r="B20" t="n">
-        <v>58119</v>
+        <v>91918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,42 +2682,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636402</v>
+        <v>636407</v>
       </c>
       <c r="R20" t="n">
-        <v>6668607</v>
+        <v>6668568</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2749,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2759,7 +2751,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133505427</v>
+        <v>133505425</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>58119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,34 +2789,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636407</v>
+        <v>636402</v>
       </c>
       <c r="R21" t="n">
-        <v>6668568</v>
+        <v>6668607</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,10 +2893,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133505424</v>
+        <v>133505434</v>
       </c>
       <c r="B22" t="n">
-        <v>57955</v>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636299</v>
+        <v>636321</v>
       </c>
       <c r="R22" t="n">
-        <v>6668569</v>
+        <v>6668644</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2973,12 +2973,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,10 +3000,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133505450</v>
+        <v>133505424</v>
       </c>
       <c r="B23" t="n">
-        <v>97370</v>
+        <v>57955</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,21 +3011,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3040,10 +3035,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636193</v>
+        <v>636299</v>
       </c>
       <c r="R23" t="n">
-        <v>6669060</v>
+        <v>6668569</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3075,7 +3070,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3085,7 +3080,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,10 +3219,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133505434</v>
+        <v>133505450</v>
       </c>
       <c r="B25" t="n">
-        <v>83307</v>
+        <v>97370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636321</v>
+        <v>636193</v>
       </c>
       <c r="R25" t="n">
-        <v>6668644</v>
+        <v>6669060</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,32 +3433,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133505436</v>
+        <v>133505441</v>
       </c>
       <c r="B27" t="n">
-        <v>8444</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636209</v>
+        <v>636414</v>
       </c>
       <c r="R27" t="n">
-        <v>6668786</v>
+        <v>6668891</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3540,10 +3540,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133505417</v>
+        <v>133505436</v>
       </c>
       <c r="B28" t="n">
-        <v>83298</v>
+        <v>8444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636242</v>
+        <v>636209</v>
       </c>
       <c r="R28" t="n">
-        <v>6668543</v>
+        <v>6668786</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3647,32 +3647,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133505441</v>
+        <v>133505417</v>
       </c>
       <c r="B29" t="n">
-        <v>57955</v>
+        <v>83298</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636414</v>
+        <v>636242</v>
       </c>
       <c r="R29" t="n">
-        <v>6668891</v>
+        <v>6668543</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4409,10 +4409,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133505446</v>
+        <v>133505422</v>
       </c>
       <c r="B36" t="n">
-        <v>83307</v>
+        <v>57955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636243</v>
+        <v>636213</v>
       </c>
       <c r="R36" t="n">
-        <v>6669054</v>
+        <v>6668594</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4489,7 +4489,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4516,10 +4521,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133505422</v>
+        <v>133505446</v>
       </c>
       <c r="B37" t="n">
-        <v>57955</v>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,21 +4532,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4551,10 +4556,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636213</v>
+        <v>636243</v>
       </c>
       <c r="R37" t="n">
-        <v>6668594</v>
+        <v>6669054</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4586,7 +4591,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4596,12 +4601,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 22547-2026 artfynd.xlsx
+++ b/artfynd/A 22547-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68585433</v>
+        <v>133505450</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N om Velången, Upl</t>
+          <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636330.7367233899</v>
+        <v>636193</v>
       </c>
       <c r="R2" t="n">
-        <v>6668599.165551153</v>
+        <v>6669060</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,41 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68585434</v>
+        <v>133505458</v>
       </c>
       <c r="B3" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101520</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N om Velången, Upl</t>
+          <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636275.8830935243</v>
+        <v>636122</v>
       </c>
       <c r="R3" t="n">
-        <v>6668596.628428144</v>
+        <v>6669062</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,84 +873,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68585437</v>
+        <v>133505418</v>
       </c>
       <c r="B4" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N om Velången, Upl</t>
+          <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636301.0411927868</v>
+        <v>636240</v>
       </c>
       <c r="R4" t="n">
-        <v>6668685.830827795</v>
+        <v>6668551</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,58 +980,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133505440</v>
+        <v>133505434</v>
       </c>
       <c r="B5" t="n">
-        <v>8449</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636418</v>
+        <v>636321</v>
       </c>
       <c r="R5" t="n">
-        <v>6668890</v>
+        <v>6668644</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133505416</v>
+        <v>133505446</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636238</v>
+        <v>636243</v>
       </c>
       <c r="R6" t="n">
-        <v>6668537</v>
+        <v>6669054</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133505428</v>
+        <v>133505427</v>
       </c>
       <c r="B7" t="n">
-        <v>92392</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1335,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133505439</v>
+        <v>133505428</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>92406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636429</v>
+        <v>636407</v>
       </c>
       <c r="R8" t="n">
-        <v>6668832</v>
+        <v>6668568</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133505455</v>
+        <v>133505432</v>
       </c>
       <c r="B9" t="n">
-        <v>5201</v>
+        <v>92406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636195</v>
+        <v>636364</v>
       </c>
       <c r="R9" t="n">
-        <v>6669061</v>
+        <v>6668635</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1549,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133505431</v>
+        <v>68585433</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,37 +1542,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora harbacken, Upl</t>
+          <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>636331</v>
       </c>
       <c r="R10" t="n">
-        <v>6668637</v>
+        <v>6668599</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,27 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,48 +1612,58 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133505445</v>
+        <v>133505430</v>
       </c>
       <c r="B11" t="n">
-        <v>8449</v>
+        <v>91995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636385</v>
+        <v>636336</v>
       </c>
       <c r="R11" t="n">
-        <v>6669003</v>
+        <v>6668597</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133505437</v>
+        <v>133505442</v>
       </c>
       <c r="B12" t="n">
-        <v>5180</v>
+        <v>91995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102204</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636297</v>
+        <v>636397</v>
       </c>
       <c r="R12" t="n">
-        <v>6668845</v>
+        <v>6668963</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133505421</v>
+        <v>133505433</v>
       </c>
       <c r="B13" t="n">
-        <v>8449</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636195</v>
+        <v>636373</v>
       </c>
       <c r="R13" t="n">
-        <v>6668569</v>
+        <v>6668624</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133505415</v>
+        <v>133505417</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>83341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636248</v>
+        <v>636242</v>
       </c>
       <c r="R14" t="n">
-        <v>6668556</v>
+        <v>6668543</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2089,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,12 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133505435</v>
+        <v>133505414</v>
       </c>
       <c r="B15" t="n">
-        <v>5181</v>
+        <v>79992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636337</v>
+        <v>636250</v>
       </c>
       <c r="R15" t="n">
-        <v>6668680</v>
+        <v>6668528</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2201,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133505418</v>
+        <v>133505422</v>
       </c>
       <c r="B16" t="n">
-        <v>83336</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636240</v>
+        <v>636213</v>
       </c>
       <c r="R16" t="n">
-        <v>6668551</v>
+        <v>6668594</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2308,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2253,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,32 +2285,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133505452</v>
+        <v>133505424</v>
       </c>
       <c r="B17" t="n">
-        <v>5180</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636195</v>
+        <v>636299</v>
       </c>
       <c r="R17" t="n">
-        <v>6669061</v>
+        <v>6668569</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2415,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2365,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,7 +2404,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2564,32 +2509,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133505442</v>
+        <v>133505431</v>
       </c>
       <c r="B19" t="n">
-        <v>91981</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636397</v>
+        <v>636331</v>
       </c>
       <c r="R19" t="n">
-        <v>6668963</v>
+        <v>6668637</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2634,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2589,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133505427</v>
+        <v>133505439</v>
       </c>
       <c r="B20" t="n">
-        <v>91960</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2706,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636407</v>
+        <v>636429</v>
       </c>
       <c r="R20" t="n">
-        <v>6668568</v>
+        <v>6668832</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2741,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,53 +2728,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133505425</v>
+        <v>133505441</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636402</v>
+        <v>636414</v>
       </c>
       <c r="R21" t="n">
-        <v>6668607</v>
+        <v>6668891</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2856,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,48 +2835,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133505434</v>
+        <v>68585436</v>
       </c>
       <c r="B22" t="n">
-        <v>83336</v>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora harbacken, Upl</t>
+          <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636321</v>
+        <v>636292</v>
       </c>
       <c r="R22" t="n">
-        <v>6668644</v>
+        <v>6668636</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2958,22 +2905,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,48 +2921,58 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133505458</v>
+        <v>133505435</v>
       </c>
       <c r="B23" t="n">
-        <v>97421</v>
+        <v>5181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3035,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636122</v>
+        <v>636337</v>
       </c>
       <c r="R23" t="n">
-        <v>6669062</v>
+        <v>6668680</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3070,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3080,7 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,32 +3054,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133505450</v>
+        <v>133505453</v>
       </c>
       <c r="B24" t="n">
-        <v>97421</v>
+        <v>5181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3142,10 +3089,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636193</v>
+        <v>636195</v>
       </c>
       <c r="R24" t="n">
-        <v>6669060</v>
+        <v>6669061</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3177,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3187,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133505424</v>
+        <v>68585434</v>
       </c>
       <c r="B25" t="n">
-        <v>57972</v>
+        <v>6275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3225,16 +3172,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>101520</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3243,19 +3190,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora harbacken, Upl</t>
+          <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636299</v>
+        <v>636276</v>
       </c>
       <c r="R25" t="n">
-        <v>6668569</v>
+        <v>6668597</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3279,27 +3231,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,26 +3247,36 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133505438</v>
+        <v>68585435</v>
       </c>
       <c r="B26" t="n">
-        <v>5201</v>
+        <v>44177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,37 +3284,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora harbacken, Upl</t>
+          <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636305</v>
+        <v>636292</v>
       </c>
       <c r="R26" t="n">
-        <v>6668862</v>
+        <v>6668636</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3391,22 +3343,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,48 +3359,58 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133505420</v>
+        <v>133505449</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>44182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3468,10 +3420,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636224</v>
+        <v>636189</v>
       </c>
       <c r="R27" t="n">
-        <v>6668560</v>
+        <v>6669067</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3503,7 +3455,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3513,12 +3465,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3545,10 +3492,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133505441</v>
+        <v>133505423</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>5180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,21 +3503,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3580,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636414</v>
+        <v>636265</v>
       </c>
       <c r="R28" t="n">
-        <v>6668891</v>
+        <v>6668598</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3615,7 +3562,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3625,7 +3572,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3652,32 +3599,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133505417</v>
+        <v>133505437</v>
       </c>
       <c r="B29" t="n">
-        <v>83327</v>
+        <v>5180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>102204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3687,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636242</v>
+        <v>636297</v>
       </c>
       <c r="R29" t="n">
-        <v>6668543</v>
+        <v>6668845</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3722,7 +3669,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3732,7 +3679,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3759,32 +3706,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133505436</v>
+        <v>133505452</v>
       </c>
       <c r="B30" t="n">
-        <v>8449</v>
+        <v>5180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>102204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3794,10 +3741,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636209</v>
+        <v>636195</v>
       </c>
       <c r="R30" t="n">
-        <v>6668786</v>
+        <v>6669061</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3829,7 +3776,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3839,7 +3786,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,56 +3813,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133505444</v>
+        <v>68585437</v>
       </c>
       <c r="B31" t="n">
-        <v>58136</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora harbacken, Upl</t>
+          <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636416</v>
+        <v>636301</v>
       </c>
       <c r="R31" t="n">
-        <v>6668962</v>
+        <v>6668686</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,22 +3883,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2017-12-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3965,48 +3899,58 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133505459</v>
+        <v>133505415</v>
       </c>
       <c r="B32" t="n">
-        <v>8449</v>
+        <v>58136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4016,10 +3960,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636129</v>
+        <v>636248</v>
       </c>
       <c r="R32" t="n">
-        <v>6668995</v>
+        <v>6668556</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4051,7 +3995,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4061,7 +4005,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4088,32 +4037,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133505449</v>
+        <v>133505420</v>
       </c>
       <c r="B33" t="n">
-        <v>44182</v>
+        <v>58136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101735</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636189</v>
+        <v>636224</v>
       </c>
       <c r="R33" t="n">
-        <v>6669067</v>
+        <v>6668560</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4158,7 +4107,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4168,7 +4117,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,45 +4149,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133505453</v>
+        <v>133505425</v>
       </c>
       <c r="B34" t="n">
-        <v>5181</v>
+        <v>58136</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636195</v>
+        <v>636402</v>
       </c>
       <c r="R34" t="n">
-        <v>6669061</v>
+        <v>6668607</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4265,7 +4227,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4275,7 +4237,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4302,45 +4264,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133505419</v>
+        <v>133505444</v>
       </c>
       <c r="B35" t="n">
-        <v>8449</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636240</v>
+        <v>636416</v>
       </c>
       <c r="R35" t="n">
-        <v>6668551</v>
+        <v>6668962</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4372,7 +4342,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4382,7 +4352,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4409,10 +4379,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133505422</v>
+        <v>133505447</v>
       </c>
       <c r="B36" t="n">
-        <v>57972</v>
+        <v>58136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4420,34 +4390,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636213</v>
+        <v>636230</v>
       </c>
       <c r="R36" t="n">
-        <v>6668594</v>
+        <v>6669046</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4479,7 +4457,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4489,12 +4467,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4521,32 +4494,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133505423</v>
+        <v>133505438</v>
       </c>
       <c r="B37" t="n">
-        <v>5180</v>
+        <v>5201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102204</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4556,10 +4529,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636265</v>
+        <v>636305</v>
       </c>
       <c r="R37" t="n">
-        <v>6668598</v>
+        <v>6668862</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4591,7 +4564,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4601,7 +4574,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4628,32 +4601,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133505446</v>
+        <v>133505455</v>
       </c>
       <c r="B38" t="n">
-        <v>83336</v>
+        <v>5201</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4663,10 +4636,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636243</v>
+        <v>636195</v>
       </c>
       <c r="R38" t="n">
-        <v>6669054</v>
+        <v>6669061</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4698,7 +4671,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4708,7 +4681,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,6 +4705,862 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133505413</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>636253</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6668530</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133505416</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>636238</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6668537</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133505419</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>636240</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6668551</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133505421</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>636195</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6668569</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133505436</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>636209</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6668786</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133505440</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>636418</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6668890</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133505445</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>636385</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6669003</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133505459</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>636129</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6668995</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
